--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488089_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488089_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.0384</v>
+        <v>11.5662</v>
       </c>
       <c r="E2" t="n">
-        <v>11.2116</v>
+        <v>9.5817</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8268</v>
+        <v>1.9845</v>
       </c>
       <c r="G2" t="n">
         <v>9.3104</v>
@@ -610,13 +610,13 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8491</v>
+        <v>2.3768</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2819</v>
+        <v>1.652</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5672</v>
+        <v>0.7248</v>
       </c>
       <c r="V2" t="n">
         <v>0.8701</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. SALAS MERCHAN</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1083</v>
+        <v>7.4004</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8577</v>
+        <v>3.9998</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2505</v>
+        <v>3.4006</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2324</v>
+        <v>4.0752</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1004</v>
+        <v>3.6275</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1319</v>
+        <v>0.4477</v>
       </c>
       <c r="J3" t="n">
-        <v>1.6748</v>
+        <v>3.9782</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5542</v>
+        <v>3.8136</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1205</v>
+        <v>0.1646</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4424</v>
+        <v>0.097</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4538</v>
+        <v>-0.1861</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0114</v>
+        <v>0.2831</v>
       </c>
       <c r="P3" t="n">
-        <v>1.784</v>
+        <v>2.1805</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.784</v>
+        <v>3.1716</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8848</v>
+        <v>0.8782</v>
       </c>
       <c r="T3" t="n">
-        <v>2.7093</v>
+        <v>0.7462</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1755</v>
+        <v>0.132</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2071</v>
+        <v>0.2666</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.9825</v>
+        <v>6.6285</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6942</v>
+        <v>4.7442</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2883</v>
+        <v>1.8843</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0752</v>
+        <v>5.3272</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6275</v>
+        <v>2.599</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4477</v>
+        <v>2.7282</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9782</v>
+        <v>6.1674</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8136</v>
+        <v>3.5922</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1646</v>
+        <v>2.5753</v>
       </c>
       <c r="M4" t="n">
-        <v>0.097</v>
+        <v>-0.8403</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1861</v>
+        <v>-0.9932</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2831</v>
+        <v>0.1529</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1716</v>
+        <v>2.5769</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4603</v>
+        <v>0.7066</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4406</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0197</v>
+        <v>0.1476</v>
       </c>
       <c r="V4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>R. SALAS MERCHAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.014</v>
+        <v>5.7826</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4386</v>
+        <v>4.2902</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5754</v>
+        <v>1.4924</v>
       </c>
       <c r="G5" t="n">
-        <v>5.3272</v>
+        <v>1.2324</v>
       </c>
       <c r="H5" t="n">
-        <v>2.599</v>
+        <v>1.1004</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7282</v>
+        <v>0.1319</v>
       </c>
       <c r="J5" t="n">
-        <v>6.1674</v>
+        <v>1.6748</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5922</v>
+        <v>1.5542</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5753</v>
+        <v>0.1205</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8403</v>
+        <v>-0.4424</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9932</v>
+        <v>-0.4538</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1529</v>
+        <v>0.0114</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5947</v>
+        <v>1.784</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5769</v>
+        <v>1.784</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0921</v>
+        <v>1.5592</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2534</v>
+        <v>1.1418</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1612</v>
+        <v>0.4174</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.6192</v>
+        <v>5.4061</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6457</v>
+        <v>2.4607</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9735</v>
+        <v>2.9454</v>
       </c>
       <c r="G6" t="n">
         <v>2.9575</v>
@@ -922,13 +922,13 @@
         <v>3.1716</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1354</v>
+        <v>0.9223</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2386</v>
+        <v>0.5764</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3739</v>
+        <v>0.3459</v>
       </c>
       <c r="V6" t="n">
         <v>0.337</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.4777</v>
+        <v>4.3421</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0804</v>
+        <v>1.9442</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3972</v>
+        <v>2.3978</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4596</v>
+        <v>4.2357</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6107</v>
+        <v>3.5871</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1511</v>
+        <v>0.6485</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2999</v>
+        <v>2.9298</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3323</v>
+        <v>2.9661</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0324</v>
+        <v>-0.0363</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8403</v>
+        <v>1.3059</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7215</v>
+        <v>0.621</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1187</v>
+        <v>0.6848</v>
       </c>
       <c r="P7" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.9822</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.9911</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-0.9911</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.9822</v>
-      </c>
       <c r="S7" t="n">
-        <v>2.9565</v>
+        <v>0.5643</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7717</v>
+        <v>0.4635</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1848</v>
+        <v>0.1008</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0704</v>
+        <v>0.5331</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2858</v>
+        <v>3.9698</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1688</v>
+        <v>3.7457</v>
       </c>
       <c r="F8" t="n">
-        <v>2.117</v>
+        <v>0.2242</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2357</v>
+        <v>1.3282</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5871</v>
+        <v>1.4793</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6485</v>
+        <v>-0.1511</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9298</v>
+        <v>2.0326</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9661</v>
+        <v>2.065</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0363</v>
+        <v>-0.0324</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3059</v>
+        <v>-0.7044</v>
       </c>
       <c r="N8" t="n">
-        <v>0.621</v>
+        <v>-0.5857</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6848</v>
+        <v>-0.1187</v>
       </c>
       <c r="P8" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.9822</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9911</v>
+        <v>1.5858</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4919</v>
+        <v>0.5029</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.312</v>
+        <v>0.6269</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.18</v>
+        <v>-0.124</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5331</v>
+        <v>1.5441</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5331</v>
+        <v>2.0772</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.0892</v>
+        <v>2.9454</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1739</v>
+        <v>1.7167</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0847</v>
+        <v>1.2288</v>
       </c>
       <c r="G9" t="n">
-        <v>1.3282</v>
+        <v>0.4596</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4793</v>
+        <v>0.6107</v>
       </c>
       <c r="I9" t="n">
         <v>-0.1511</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0326</v>
+        <v>1.2999</v>
       </c>
       <c r="K9" t="n">
-        <v>2.065</v>
+        <v>1.3323</v>
       </c>
       <c r="L9" t="n">
         <v>-0.0324</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7044</v>
+        <v>-0.8403</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5857</v>
+        <v>-0.7215</v>
       </c>
       <c r="O9" t="n">
         <v>-0.1187</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3777</v>
+        <v>1.4243</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0552</v>
+        <v>1.4079</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4329</v>
+        <v>0.0164</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5441</v>
+        <v>0.0704</v>
       </c>
       <c r="W9" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5331</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="10">
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. JIMENEZ EXPOSITO</t>
+          <t>J. CEBOLLA HERRERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.2533</v>
+        <v>1.2829</v>
       </c>
       <c r="E11" t="n">
-        <v>1.2857</v>
+        <v>-0.843</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0324</v>
+        <v>2.1259</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6083</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.066</v>
+        <v>0.3996</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8839</v>
+        <v>0.2087</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2857</v>
+        <v>-0.1621</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="L11" t="n">
-        <v>1.2857</v>
+        <v>-0.7478</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4677</v>
+        <v>0.7704</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.066</v>
+        <v>-0.1861</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4018</v>
+        <v>0.9565</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1982</v>
+        <v>2.5769</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2371</v>
+        <v>0.5625</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>0.3103</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2371</v>
+        <v>0.2523</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ÁVALOS ORTIZ</t>
+          <t>D. JIMENEZ EXPOSITO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9053</v>
+        <v>1.2428</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9053</v>
+        <v>1.3876</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0.1447</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9053</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3027</v>
+        <v>-0.066</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6027</v>
+        <v>0.8839</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9053</v>
+        <v>1.2857</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6027</v>
+        <v>1.2857</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-0.4677</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>-0.066</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.4018</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>0.2267</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>0.1019</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.1248</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRÍGUEZ</t>
+          <t>P. ÁVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3027</v>
+        <v>0.9053</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3027</v>
+        <v>0.9053</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3027</v>
+        <v>0.9053</v>
       </c>
       <c r="H13" t="n">
         <v>0.3027</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3027</v>
+        <v>0.9053</v>
       </c>
       <c r="K13" t="n">
         <v>0.3027</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CEBOLLA HERRERA</t>
+          <t>L. SIGISMONTI RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1944</v>
+        <v>0.3027</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4542</v>
+        <v>0.3027</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6485</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6083</v>
+        <v>0.3027</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3996</v>
+        <v>0.3027</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2087</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1621</v>
+        <v>0.3027</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5857</v>
+        <v>0.3027</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7478</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7704</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1861</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9565</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5769</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.526</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.301</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2251</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.3206</v>
+        <v>0.1255</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.2888</v>
+        <v>-1.2077</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9681999999999999</v>
+        <v>1.3332</v>
       </c>
       <c r="G15" t="n">
         <v>0.7701</v>
@@ -1624,13 +1624,13 @@
         <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0818</v>
+        <v>0.3643</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3744</v>
+        <v>0.7067</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7074</v>
+        <v>-0.3424</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2071</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.9314</v>
+        <v>-2.5697</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8121</v>
+        <v>-0.5065</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1193</v>
+        <v>-2.0632</v>
       </c>
       <c r="G16" t="n">
         <v>-3.1892</v>
@@ -1702,13 +1702,13 @@
         <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3369</v>
+        <v>0.0248</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3744</v>
+        <v>-0.0688</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>50.82680000000001</v>
+        <v>51.1386</v>
       </c>
       <c r="E17" t="n">
-        <v>34.01749999999999</v>
+        <v>34.32959999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>16.809</v>
+        <v>16.8092</v>
       </c>
       <c r="G17" t="n">
         <v>30.9494</v>
@@ -1762,13 +1762,13 @@
         <v>9.930500000000002</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.716299999999999</v>
+        <v>-3.7163</v>
       </c>
       <c r="N17" t="n">
         <v>-4.5382</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8217000000000002</v>
+        <v>0.8217</v>
       </c>
       <c r="P17" t="n">
         <v>7.929</v>
@@ -1780,13 +1780,13 @@
         <v>23.7868</v>
       </c>
       <c r="S17" t="n">
-        <v>9.801000000000002</v>
+        <v>10.1129</v>
       </c>
       <c r="T17" t="n">
-        <v>7.9117</v>
+        <v>8.223800000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>1.889</v>
+        <v>1.8892</v>
       </c>
       <c r="V17" t="n">
         <v>2.1476</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.2677</v>
+        <v>-0.9386</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2113</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0564</v>
+        <v>-1.0329</v>
       </c>
       <c r="G18" t="n">
         <v>1.3408</v>
@@ -1858,13 +1858,13 @@
         <v>0.5947</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5668</v>
+        <v>-0.2377</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.301</v>
+        <v>0.0047</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2659</v>
+        <v>-0.2423</v>
       </c>
       <c r="V18" t="n">
         <v>0.337</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2224</v>
+        <v>-2.8232</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3979</v>
+        <v>-1.111</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8245</v>
+        <v>-1.7121</v>
       </c>
       <c r="G19" t="n">
         <v>-4.4157</v>
@@ -1936,13 +1936,13 @@
         <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0566</v>
+        <v>-0.5442</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8701</v>
+        <v>0.157</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8135</v>
+        <v>-0.7012</v>
       </c>
       <c r="V19" t="n">
         <v>1.7403</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9797</v>
+        <v>-3.1268</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1602</v>
+        <v>-1.482</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8195</v>
+        <v>-1.6448</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5429</v>
+        <v>-3.8894</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.2363</v>
+        <v>-1.7678</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3067</v>
+        <v>-2.1216</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5986</v>
+        <v>-0.948</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0404</v>
+        <v>1.0492</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.639</v>
+        <v>-1.9972</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9443</v>
+        <v>-2.9414</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2766</v>
+        <v>-2.817</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6677</v>
+        <v>-0.1244</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3964</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1579</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4295</v>
+        <v>-0.534</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2717</v>
+        <v>-0.2891</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.326</v>
+        <v>-3.2853</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6857</v>
+        <v>-1.4658</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6402</v>
+        <v>-1.8195</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.8894</v>
+        <v>-2.5429</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7678</v>
+        <v>-1.2363</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1216</v>
+        <v>-1.3067</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.948</v>
+        <v>-0.5986</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0492</v>
+        <v>0.0404</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9972</v>
+        <v>-0.639</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9414</v>
+        <v>-1.9443</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.817</v>
+        <v>-1.2766</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1244</v>
+        <v>-0.6677</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5858</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0223</v>
+        <v>-0.1477</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7377</v>
+        <v>0.1239</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2846</v>
+        <v>-0.2717</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3507</v>
+        <v>-4.1365</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9369</v>
+        <v>-2.835</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4138</v>
+        <v>-1.3015</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4544</v>
@@ -2170,13 +2170,13 @@
         <v>0.9911</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9052</v>
+        <v>-0.6909999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4684</v>
+        <v>-0.3561</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2476</v>
+        <v>-5.1039</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6869</v>
+        <v>-1.635</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.9345</v>
+        <v>-3.4689</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.6117</v>
+        <v>-1.3023</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9395</v>
+        <v>-1.1206</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6722</v>
+        <v>-0.1817</v>
       </c>
       <c r="J23" t="n">
-        <v>2.524</v>
+        <v>2.4955</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4761</v>
+        <v>0.6797</v>
       </c>
       <c r="L23" t="n">
-        <v>0.048</v>
+        <v>1.8158</v>
       </c>
       <c r="M23" t="n">
-        <v>-6.1357</v>
+        <v>-3.7978</v>
       </c>
       <c r="N23" t="n">
-        <v>-4.4155</v>
+        <v>-1.8003</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7201</v>
+        <v>-1.9975</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1982</v>
+        <v>-2.5769</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R23" t="n">
-        <v>2.7751</v>
+        <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2969</v>
+        <v>-0.9581</v>
       </c>
       <c r="T23" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.166</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3668</v>
+        <v>-0.7921</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1408</v>
+        <v>-0.2666</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0663</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2482</v>
+        <v>-5.1924</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1443</v>
+        <v>-0.4117</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.1039</v>
+        <v>-4.7807</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.3023</v>
+        <v>-4.4654</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1206</v>
+        <v>-1.5729</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1817</v>
+        <v>-2.8925</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4955</v>
+        <v>0.5255</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6797</v>
+        <v>1.4263</v>
       </c>
       <c r="L24" t="n">
-        <v>1.8158</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.7978</v>
+        <v>-4.991</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.8003</v>
+        <v>-2.9992</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.9975</v>
+        <v>-1.9918</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.5769</v>
+        <v>1.1893</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.1024</v>
+        <v>-1.5793</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6753</v>
+        <v>-0.2127</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4271</v>
+        <v>-1.3666</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2666</v>
+        <v>-0.337</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2666</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.2858</v>
+        <v>-5.5355</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0043</v>
+        <v>0.4832</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.2815</v>
+        <v>-6.0187</v>
       </c>
       <c r="G25" t="n">
-        <v>-4.4654</v>
+        <v>-3.6117</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.5729</v>
+        <v>-1.9395</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.8925</v>
+        <v>-1.6722</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5255</v>
+        <v>2.524</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4263</v>
+        <v>2.4761</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.9006999999999999</v>
+        <v>0.048</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.991</v>
+        <v>-6.1357</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.9992</v>
+        <v>-4.4155</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.9918</v>
+        <v>-1.7201</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1893</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1805</v>
+        <v>2.7751</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6727</v>
+        <v>-1.5848</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1948</v>
+        <v>-0.1338</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.8675</v>
+        <v>-1.4511</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.337</v>
+        <v>-0.1408</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2666</v>
+        <v>1.0663</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.0376</v>
+        <v>-6.2136</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.4472</v>
+        <v>-2.0398</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.5904</v>
+        <v>-4.1738</v>
       </c>
       <c r="G26" t="n">
         <v>-3.468</v>
@@ -2482,13 +2482,13 @@
         <v>1.5858</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.6995</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8625</v>
+        <v>-0.4551</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.837</v>
+        <v>-0.4204</v>
       </c>
       <c r="V26" t="n">
         <v>-1.4737</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-10.7038</v>
+        <v>-11.3276</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.9813</v>
+        <v>-6.2869</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.7225</v>
+        <v>-5.0407</v>
       </c>
       <c r="G27" t="n">
         <v>-3.6962</v>
@@ -2560,13 +2560,13 @@
         <v>1.9822</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.0451</v>
+        <v>-0.669</v>
       </c>
       <c r="T27" t="n">
-        <v>0.3085</v>
+        <v>0.0029</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3537</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-2.0068</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-47.6695</v>
+        <v>-47.68340000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-16.2822</v>
+        <v>-16.6897</v>
       </c>
       <c r="F28" t="n">
-        <v>-31.3872</v>
+        <v>-30.9936</v>
       </c>
       <c r="G28" t="n">
         <v>-28.5052</v>
@@ -2638,13 +2638,13 @@
         <v>14.8668</v>
       </c>
       <c r="S28" t="n">
-        <v>-8.096399999999999</v>
+        <v>-8.1104</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.1404</v>
+        <v>-1.548</v>
       </c>
       <c r="U28" t="n">
-        <v>-6.956199999999999</v>
+        <v>-6.5625</v>
       </c>
       <c r="V28" t="n">
         <v>-2.1476</v>
